--- a/ejemplo_clientes.xlsx
+++ b/ejemplo_clientes.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -545,6 +545,36 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SOFIA DUARTE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FORD RANGER XLT 3.2 D/C 4X4 AT 2019</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3790000008</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>JUAN PEREZZ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3790000007</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
